--- a/Outputs/Scenarios/PtX_demand_SE_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SE_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.004466517697420779</v>
       </c>
       <c r="K16" t="n">
-        <v>0.005833138430388838</v>
+        <v>0.006475259306487511</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.001296853546147529</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01166627686077768</v>
+        <v>0.01037482836918023</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>6.435495947338796e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00194437947679628</v>
+        <v>0.001296853546147529</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.006612135668584872</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03143247463308507</v>
+        <v>0.03489260992563983</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.006988230551797708</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.06286494926617014</v>
+        <v>0.05590584441438166</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0003480071404518354</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01047749154436169</v>
+        <v>0.006988230551797708</v>
       </c>
     </row>
     <row r="43">
